--- a/scripts/productos-digitales/guia-pasteleria/build/capacidad-obrador-y-local.xlsx
+++ b/scripts/productos-digitales/guia-pasteleria/build/capacidad-obrador-y-local.xlsx
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>Sammic BP-20, 900 W. Es la que marca el ritmo de cremas, mousses y merengues, no de las masas.</t>
+          <t>Sammic BE-20, 900 W. Es la que marca el ritmo de cremas, mousses y merengues, no de las masas.</t>
         </is>
       </c>
     </row>
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>El pico que decide el año. Referencias de escala, nunca de precio ni de cuota: PS-35 (unos 30 millones de roscones en España en la campaña 2025/26), PS-36 (más de 2,9 millones en la Comunidad de Madrid) y PS-38 (El Corte Inglés 850.000, Viena Capellanes 72.000). PS-46: el supermercado entra con roscones premiados a 9 €. El roscón relleno de nata arrastra los 4 °C de la fila 9 y las 24 h del art. 9.3 justo el día de más producción: eso limita la producción tanto como el horno.</t>
+          <t>El pico que decide el año. Las unidades de campaña son las de los CINCO días de más venta: 160 al día, 800 en total, el 47 % de los roscones que el mix de la carta asigna al año (1,2 % de las piezas). El resto se venden en la semana previa, fuera de la ventana de campaña, y por eso no entran en esta fila. Referencias de escala, nunca de precio ni de cuota: PS-35 (unos 30 millones de roscones en España en la campaña 2025/26), PS-36 (más de 2,9 millones en la Comunidad de Madrid) y PS-38 (El Corte Inglés 850.000, Viena Capellanes 72.000). PS-46: el supermercado entra con roscones premiados a 9 €. El roscón relleno de nata arrastra los 4 °C de la fila 9 y las 24 h del art. 9.3 justo el día de más producción: eso limita la producción tanto como el horno.</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Ocho días seguidos de producción extra, que es más agotador que los cinco de Reyes aunque el pico sea menor. Torrijas y monas a la vez: una necesita freidora y frío, la otra horno y chocolate.</t>
+          <t>Ocho días seguidos de producción extra, que es más agotador que los cinco de Reyes aunque el pico sea menor. Torrijas y monas a la vez: una necesita freidora y frío, la otra horno y chocolate. Son 230 torrijas al día y 1.840 en la campaña: el 99 % de las que el mix de la carta asigna al año, porque fuera de Semana Santa no se hacen.</t>
         </is>
       </c>
     </row>
@@ -3496,11 +3496,11 @@
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Tres días con tres referencias que sólo se hacen ahora: buñuelos, huesos de santo y panellets. Los buñuelos van rellenos (4 °C y 24 h) y los otros dos son estables a temperatura ambiente: por eso los buñuelos se hacen el mismo día y los huesos de santo se pueden adelantar. Ese detalle legal ES la planificación de la campaña.</t>
+          <t>Tres días con tres referencias que sólo se hacen ahora: buñuelos, huesos de santo y panellets. Los buñuelos van rellenos (4 °C y 24 h) y los otros dos son estables a temperatura ambiente: por eso los buñuelos se hacen el mismo día y los huesos de santo se pueden adelantar. Ese detalle legal ES la planificación de la campaña. Son 470 buñuelos al día y 1.410 en los tres días: el 99 % de los que el mix de la carta asigna al año, porque fuera de esta fecha no se hacen.</t>
         </is>
       </c>
     </row>
